--- a/data/nzd0162/nzd0162.xlsx
+++ b/data/nzd0162/nzd0162.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I390"/>
+  <dimension ref="A1:I392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13286,6 +13286,72 @@
         <v>356.05</v>
       </c>
       <c r="I390" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>315.25</v>
+      </c>
+      <c r="C391" t="n">
+        <v>355.77</v>
+      </c>
+      <c r="D391" t="n">
+        <v>354.4</v>
+      </c>
+      <c r="E391" t="n">
+        <v>363.19</v>
+      </c>
+      <c r="F391" t="n">
+        <v>365.16</v>
+      </c>
+      <c r="G391" t="n">
+        <v>348.56</v>
+      </c>
+      <c r="H391" t="n">
+        <v>355.68</v>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>318.51</v>
+      </c>
+      <c r="C392" t="n">
+        <v>353.25</v>
+      </c>
+      <c r="D392" t="n">
+        <v>353.34</v>
+      </c>
+      <c r="E392" t="n">
+        <v>363.28</v>
+      </c>
+      <c r="F392" t="n">
+        <v>364.34</v>
+      </c>
+      <c r="G392" t="n">
+        <v>348.01</v>
+      </c>
+      <c r="H392" t="n">
+        <v>354.77</v>
+      </c>
+      <c r="I392" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -13302,7 +13368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B410"/>
+  <dimension ref="A1:B412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17405,6 +17471,26 @@
       </c>
       <c r="B410" t="n">
         <v>-0.4</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>
@@ -17573,28 +17659,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.210920882307134</v>
+        <v>-0.20387465198944</v>
       </c>
       <c r="J2" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="K2" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01965090393645963</v>
+        <v>0.01856561479292218</v>
       </c>
       <c r="M2" t="n">
-        <v>9.486407764592526</v>
+        <v>9.47446877472813</v>
       </c>
       <c r="N2" t="n">
-        <v>119.3715042417485</v>
+        <v>118.9874148701964</v>
       </c>
       <c r="O2" t="n">
-        <v>10.92572671458281</v>
+        <v>10.90813526090488</v>
       </c>
       <c r="P2" t="n">
-        <v>315.8317342418472</v>
+        <v>315.7591675416996</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17651,28 +17737,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1042883475654005</v>
+        <v>-0.1028315939193503</v>
       </c>
       <c r="J3" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="K3" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01465134882087238</v>
+        <v>0.01440850922609582</v>
       </c>
       <c r="M3" t="n">
-        <v>4.901386093735845</v>
+        <v>4.882551449599916</v>
       </c>
       <c r="N3" t="n">
-        <v>39.92662457121776</v>
+        <v>39.74047185052829</v>
       </c>
       <c r="O3" t="n">
-        <v>6.318751820669788</v>
+        <v>6.304004429767502</v>
       </c>
       <c r="P3" t="n">
-        <v>355.8444917362464</v>
+        <v>355.8295865617081</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17729,28 +17815,28 @@
         <v>0.1265</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.00139587636130776</v>
+        <v>-0.004941254317311754</v>
       </c>
       <c r="J4" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="K4" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L4" t="n">
-        <v>7.005132838244776e-06</v>
+        <v>8.844678572350606e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>2.99490288857439</v>
+        <v>2.998844574102518</v>
       </c>
       <c r="N4" t="n">
-        <v>15.13033999154769</v>
+        <v>15.11296802857929</v>
       </c>
       <c r="O4" t="n">
-        <v>3.889773771255558</v>
+        <v>3.887540099931997</v>
       </c>
       <c r="P4" t="n">
-        <v>357.3240427719368</v>
+        <v>357.3604543962256</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17807,28 +17893,28 @@
         <v>0.065</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04327398885341694</v>
+        <v>0.04443525933512477</v>
       </c>
       <c r="J5" t="n">
+        <v>391</v>
+      </c>
+      <c r="K5" t="n">
         <v>389</v>
       </c>
-      <c r="K5" t="n">
-        <v>387</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.004313853773595278</v>
+        <v>0.004599385581002924</v>
       </c>
       <c r="M5" t="n">
-        <v>3.811927210224518</v>
+        <v>3.797505346288631</v>
       </c>
       <c r="N5" t="n">
-        <v>23.31547156096408</v>
+        <v>23.20183772823302</v>
       </c>
       <c r="O5" t="n">
-        <v>4.828609692340445</v>
+        <v>4.816828596517944</v>
       </c>
       <c r="P5" t="n">
-        <v>360.9870563047286</v>
+        <v>360.9750575480546</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17885,28 +17971,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04709242395064189</v>
+        <v>-0.04122835483711981</v>
       </c>
       <c r="J6" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="K6" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003947513751077159</v>
+        <v>0.003047524879436714</v>
       </c>
       <c r="M6" t="n">
-        <v>4.489489762147326</v>
+        <v>4.491660323799843</v>
       </c>
       <c r="N6" t="n">
-        <v>30.43931408040772</v>
+        <v>30.44493315366543</v>
       </c>
       <c r="O6" t="n">
-        <v>5.51718352788882</v>
+        <v>5.517692738243534</v>
       </c>
       <c r="P6" t="n">
-        <v>360.3363194168315</v>
+        <v>360.2761009786188</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17963,28 +18049,28 @@
         <v>0.0658</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0589670087631775</v>
+        <v>-0.05596262607392422</v>
       </c>
       <c r="J7" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="K7" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005092221620162429</v>
+        <v>0.00463716079340204</v>
       </c>
       <c r="M7" t="n">
-        <v>4.699954504508291</v>
+        <v>4.690769038410447</v>
       </c>
       <c r="N7" t="n">
-        <v>36.77695470270582</v>
+        <v>36.63063281945602</v>
       </c>
       <c r="O7" t="n">
-        <v>6.064400605394224</v>
+        <v>6.052324579816917</v>
       </c>
       <c r="P7" t="n">
-        <v>346.9543668403882</v>
+        <v>346.9234277951364</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18041,28 +18127,28 @@
         <v>0.0572</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.03966669464198465</v>
+        <v>-0.03801868815618289</v>
       </c>
       <c r="J8" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="K8" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002170174227202892</v>
+        <v>0.002016606009538235</v>
       </c>
       <c r="M8" t="n">
-        <v>4.587564737141865</v>
+        <v>4.571587982431531</v>
       </c>
       <c r="N8" t="n">
-        <v>39.1648028819307</v>
+        <v>38.97763594460443</v>
       </c>
       <c r="O8" t="n">
-        <v>6.258178879029482</v>
+        <v>6.243207184180614</v>
       </c>
       <c r="P8" t="n">
-        <v>354.6882883028398</v>
+        <v>354.6713187338254</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18100,7 +18186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I390"/>
+  <dimension ref="A1:I392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36385,6 +36471,100 @@
         </is>
       </c>
     </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>-36.73750633365892,175.81123498221416</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>-36.73754276232013,175.8102395357225</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>-36.7375456940609,175.80933275913037</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>-36.73767218358891,175.80844768095312</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>-36.73787701648186,175.8075997663709</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>-36.73806441095083,175.80671055063547</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>-36.73848555731798,175.80597648500787</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>-36.73753326911803,175.8112204493385</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>-36.737520435680985,175.81024462828992</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>-36.737536166500625,175.8093319773927</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>-36.73767297983145,175.8084478703725</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>-36.737870176817175,175.80759630114167</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>-36.738060106740704,175.80670750238173</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>-36.73847858237501,175.80597113463165</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0162/nzd0162.xlsx
+++ b/data/nzd0162/nzd0162.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I392"/>
+  <dimension ref="A1:I393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13354,6 +13354,39 @@
       <c r="I392" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:06:16+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>324.96</v>
+      </c>
+      <c r="C393" t="n">
+        <v>352.39</v>
+      </c>
+      <c r="D393" t="n">
+        <v>352.99</v>
+      </c>
+      <c r="E393" t="n">
+        <v>362.15</v>
+      </c>
+      <c r="F393" t="n">
+        <v>363.61</v>
+      </c>
+      <c r="G393" t="n">
+        <v>347.78</v>
+      </c>
+      <c r="H393" t="n">
+        <v>356.45</v>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13368,7 +13401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B412"/>
+  <dimension ref="A1:B413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17491,6 +17524,16 @@
       </c>
       <c r="B412" t="n">
         <v>0.52</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -17659,28 +17702,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.20387465198944</v>
+        <v>-0.1961055454228688</v>
       </c>
       <c r="J2" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K2" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01856561479292218</v>
+        <v>0.01722525985199519</v>
       </c>
       <c r="M2" t="n">
-        <v>9.47446877472813</v>
+        <v>9.490753349769495</v>
       </c>
       <c r="N2" t="n">
-        <v>118.9874148701964</v>
+        <v>119.2248057878603</v>
       </c>
       <c r="O2" t="n">
-        <v>10.90813526090488</v>
+        <v>10.9190112092561</v>
       </c>
       <c r="P2" t="n">
-        <v>315.7591675416996</v>
+        <v>315.6789069175866</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17737,28 +17780,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1028315939193503</v>
+        <v>-0.1032086567991086</v>
       </c>
       <c r="J3" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K3" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01440850922609582</v>
+        <v>0.01459551871672249</v>
       </c>
       <c r="M3" t="n">
-        <v>4.882551449599916</v>
+        <v>4.872191310199826</v>
       </c>
       <c r="N3" t="n">
-        <v>39.74047185052829</v>
+        <v>39.64044054925329</v>
       </c>
       <c r="O3" t="n">
-        <v>6.304004429767502</v>
+        <v>6.296065481652275</v>
       </c>
       <c r="P3" t="n">
-        <v>355.8295865617081</v>
+        <v>355.8334589905072</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17815,28 +17858,28 @@
         <v>0.1265</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.004941254317311754</v>
+        <v>-0.007141510802269872</v>
       </c>
       <c r="J4" t="n">
+        <v>392</v>
+      </c>
+      <c r="K4" t="n">
         <v>391</v>
       </c>
-      <c r="K4" t="n">
-        <v>390</v>
-      </c>
       <c r="L4" t="n">
-        <v>8.844678572350606e-05</v>
+        <v>0.0001852474265877646</v>
       </c>
       <c r="M4" t="n">
-        <v>2.998844574102518</v>
+        <v>3.003114801565139</v>
       </c>
       <c r="N4" t="n">
-        <v>15.11296802857929</v>
+        <v>15.12000073136939</v>
       </c>
       <c r="O4" t="n">
-        <v>3.887540099931997</v>
+        <v>3.888444513088671</v>
       </c>
       <c r="P4" t="n">
-        <v>357.3604543962256</v>
+        <v>357.3831243511267</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17893,28 +17936,28 @@
         <v>0.065</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04443525933512477</v>
+        <v>0.04443794437270481</v>
       </c>
       <c r="J5" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K5" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004599385581002924</v>
+        <v>0.004626694119158614</v>
       </c>
       <c r="M5" t="n">
-        <v>3.797505346288631</v>
+        <v>3.787780004174043</v>
       </c>
       <c r="N5" t="n">
-        <v>23.20183772823302</v>
+        <v>23.14234590382913</v>
       </c>
       <c r="O5" t="n">
-        <v>4.816828596517944</v>
+        <v>4.810649218538921</v>
       </c>
       <c r="P5" t="n">
-        <v>360.9750575480546</v>
+        <v>360.9750297146452</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17971,28 +18014,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04122835483711981</v>
+        <v>-0.03893634692658214</v>
       </c>
       <c r="J6" t="n">
+        <v>392</v>
+      </c>
+      <c r="K6" t="n">
         <v>391</v>
       </c>
-      <c r="K6" t="n">
-        <v>390</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.003047524879436714</v>
+        <v>0.002730335340960011</v>
       </c>
       <c r="M6" t="n">
-        <v>4.491660323799843</v>
+        <v>4.490109810624361</v>
       </c>
       <c r="N6" t="n">
-        <v>30.44493315366543</v>
+        <v>30.41664325375092</v>
       </c>
       <c r="O6" t="n">
-        <v>5.517692738243534</v>
+        <v>5.51512857998351</v>
       </c>
       <c r="P6" t="n">
-        <v>360.2761009786188</v>
+        <v>360.2524856790752</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18049,28 +18092,28 @@
         <v>0.0658</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.05596262607392422</v>
+        <v>-0.05475007573194128</v>
       </c>
       <c r="J7" t="n">
+        <v>392</v>
+      </c>
+      <c r="K7" t="n">
         <v>391</v>
       </c>
-      <c r="K7" t="n">
-        <v>390</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.00463716079340204</v>
+        <v>0.004463400186986877</v>
       </c>
       <c r="M7" t="n">
-        <v>4.690769038410447</v>
+        <v>4.684819901159572</v>
       </c>
       <c r="N7" t="n">
-        <v>36.63063281945602</v>
+        <v>36.55071545589922</v>
       </c>
       <c r="O7" t="n">
-        <v>6.052324579816917</v>
+        <v>6.045718770824459</v>
       </c>
       <c r="P7" t="n">
-        <v>346.9234277951364</v>
+        <v>346.910899427208</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18127,28 +18170,28 @@
         <v>0.0572</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.03801868815618289</v>
+        <v>-0.03656990550304982</v>
       </c>
       <c r="J8" t="n">
+        <v>392</v>
+      </c>
+      <c r="K8" t="n">
         <v>391</v>
       </c>
-      <c r="K8" t="n">
-        <v>390</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.002016606009538235</v>
+        <v>0.001876049725372142</v>
       </c>
       <c r="M8" t="n">
-        <v>4.571587982431531</v>
+        <v>4.566464425190524</v>
       </c>
       <c r="N8" t="n">
-        <v>38.97763594460443</v>
+        <v>38.89760285287797</v>
       </c>
       <c r="O8" t="n">
-        <v>6.243207184180614</v>
+        <v>6.236794276940516</v>
       </c>
       <c r="P8" t="n">
-        <v>354.6713187338254</v>
+        <v>354.656349555641</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18186,7 +18229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I392"/>
+  <dimension ref="A1:I393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36565,6 +36608,53 @@
         </is>
       </c>
     </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:06:16+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>-36.7375865616632,175.81119169561427</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>-36.73751281627233,175.81024636622902</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>-36.73753302060807,175.80933171927182</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>-36.73766298256403,175.80844549210732</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>-36.73786408784726,175.80759321624302</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>-36.73805830679827,175.80670622765754</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>-36.73849145919257,175.80598101225007</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0162/nzd0162.xlsx
+++ b/data/nzd0162/nzd0162.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I393"/>
+  <dimension ref="A1:I395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13385,6 +13385,72 @@
         <v>356.45</v>
       </c>
       <c r="I393" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>330.55</v>
+      </c>
+      <c r="C394" t="n">
+        <v>356.24</v>
+      </c>
+      <c r="D394" t="n">
+        <v>353.67</v>
+      </c>
+      <c r="E394" t="n">
+        <v>363.11</v>
+      </c>
+      <c r="F394" t="n">
+        <v>364.63</v>
+      </c>
+      <c r="G394" t="n">
+        <v>347.77</v>
+      </c>
+      <c r="H394" t="n">
+        <v>354.33</v>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>327.94</v>
+      </c>
+      <c r="C395" t="n">
+        <v>354.58</v>
+      </c>
+      <c r="D395" t="n">
+        <v>355.05</v>
+      </c>
+      <c r="E395" t="n">
+        <v>365.2</v>
+      </c>
+      <c r="F395" t="n">
+        <v>365.18</v>
+      </c>
+      <c r="G395" t="n">
+        <v>348.45</v>
+      </c>
+      <c r="H395" t="n">
+        <v>355.29</v>
+      </c>
+      <c r="I395" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13401,7 +13467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B413"/>
+  <dimension ref="A1:B415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17534,6 +17600,26 @@
       </c>
       <c r="B413" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>0.78</v>
       </c>
     </row>
   </sheetData>
@@ -17702,28 +17788,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1961055454228688</v>
+        <v>-0.1763181929152058</v>
       </c>
       <c r="J2" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K2" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01722525985199519</v>
+        <v>0.01392885362314966</v>
       </c>
       <c r="M2" t="n">
-        <v>9.490753349769495</v>
+        <v>9.546349690922151</v>
       </c>
       <c r="N2" t="n">
-        <v>119.2248057878603</v>
+        <v>120.4011570315934</v>
       </c>
       <c r="O2" t="n">
-        <v>10.9190112092561</v>
+        <v>10.97274610257585</v>
       </c>
       <c r="P2" t="n">
-        <v>315.6789069175866</v>
+        <v>315.4738405235319</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17780,28 +17866,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1032086567991086</v>
+        <v>-0.1008535282843455</v>
       </c>
       <c r="J3" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K3" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01459551871672249</v>
+        <v>0.01409560892451223</v>
       </c>
       <c r="M3" t="n">
-        <v>4.872191310199826</v>
+        <v>4.857528469195231</v>
       </c>
       <c r="N3" t="n">
-        <v>39.64044054925329</v>
+        <v>39.46917153705325</v>
       </c>
       <c r="O3" t="n">
-        <v>6.296065481652275</v>
+        <v>6.282449485435856</v>
       </c>
       <c r="P3" t="n">
-        <v>355.8334589905072</v>
+        <v>355.8091966731832</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17858,28 +17944,28 @@
         <v>0.1265</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.007141510802269872</v>
+        <v>-0.01005077340217508</v>
       </c>
       <c r="J4" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K4" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001852474265877646</v>
+        <v>0.0003700749246580148</v>
       </c>
       <c r="M4" t="n">
-        <v>3.003114801565139</v>
+        <v>3.003448351621909</v>
       </c>
       <c r="N4" t="n">
-        <v>15.12000073136939</v>
+        <v>15.08568185921018</v>
       </c>
       <c r="O4" t="n">
-        <v>3.888444513088671</v>
+        <v>3.884029075484654</v>
       </c>
       <c r="P4" t="n">
-        <v>357.3831243511267</v>
+        <v>357.4131941176894</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17936,28 +18022,28 @@
         <v>0.065</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04443794437270481</v>
+        <v>0.04650949959944533</v>
       </c>
       <c r="J5" t="n">
+        <v>394</v>
+      </c>
+      <c r="K5" t="n">
         <v>392</v>
       </c>
-      <c r="K5" t="n">
-        <v>390</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.004626694119158614</v>
+        <v>0.005119110985784103</v>
       </c>
       <c r="M5" t="n">
-        <v>3.787780004174043</v>
+        <v>3.777621669515018</v>
       </c>
       <c r="N5" t="n">
-        <v>23.14234590382913</v>
+        <v>23.0499580178095</v>
       </c>
       <c r="O5" t="n">
-        <v>4.810649218538921</v>
+        <v>4.801037181465011</v>
       </c>
       <c r="P5" t="n">
-        <v>360.9750297146452</v>
+        <v>360.9534806891309</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18014,28 +18100,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03893634692658214</v>
+        <v>-0.03309968226138744</v>
       </c>
       <c r="J6" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K6" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002730335340960011</v>
+        <v>0.001986938698274265</v>
       </c>
       <c r="M6" t="n">
-        <v>4.490109810624361</v>
+        <v>4.492270038100495</v>
       </c>
       <c r="N6" t="n">
-        <v>30.41664325375092</v>
+        <v>30.42396397118129</v>
       </c>
       <c r="O6" t="n">
-        <v>5.51512857998351</v>
+        <v>5.515792234229031</v>
       </c>
       <c r="P6" t="n">
-        <v>360.2524856790752</v>
+        <v>360.1921503661264</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18092,28 +18178,28 @@
         <v>0.0658</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.05475007573194128</v>
+        <v>-0.05202063343164864</v>
       </c>
       <c r="J7" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K7" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004463400186986877</v>
+        <v>0.004074125733207756</v>
       </c>
       <c r="M7" t="n">
-        <v>4.684819901159572</v>
+        <v>4.674424623946707</v>
       </c>
       <c r="N7" t="n">
-        <v>36.55071545589922</v>
+        <v>36.40039714693152</v>
       </c>
       <c r="O7" t="n">
-        <v>6.045718770824459</v>
+        <v>6.033274164741026</v>
       </c>
       <c r="P7" t="n">
-        <v>346.910899427208</v>
+        <v>346.8826046419777</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18170,28 +18256,28 @@
         <v>0.0572</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.03656990550304982</v>
+        <v>-0.03541651362550152</v>
       </c>
       <c r="J8" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K8" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001876049725372142</v>
+        <v>0.001779957603034177</v>
       </c>
       <c r="M8" t="n">
-        <v>4.566464425190524</v>
+        <v>4.548386960801151</v>
       </c>
       <c r="N8" t="n">
-        <v>38.89760285287797</v>
+        <v>38.70708839873358</v>
       </c>
       <c r="O8" t="n">
-        <v>6.236794276940516</v>
+        <v>6.221502101481087</v>
       </c>
       <c r="P8" t="n">
-        <v>354.656349555641</v>
+        <v>354.644391232518</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18229,7 +18315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I393"/>
+  <dimension ref="A1:I395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36655,6 +36741,100 @@
         </is>
       </c>
     </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>-36.73763274853109,175.81116677568932</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>-36.73754692641551,175.810238585918</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>-36.73753913262788,175.80933222076385</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>-36.73767147581778,175.80844751258036</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>-36.73787259572298,175.8075975266495</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>-36.738058228539906,175.80670617223478</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>-36.73847520987501,175.8059685476369</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>-36.737611183643374,175.8111784109351</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>-36.737532219185,175.81024194054635</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>-36.73755153643276,175.8093332384979</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>-36.73768996633869,175.80845191132025</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>-36.737877183302956,175.80759985088872</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>-36.73806355010881,175.8067099409847</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>-36.738482568056746,175.80597419198935</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0162/nzd0162.xlsx
+++ b/data/nzd0162/nzd0162.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I395"/>
+  <dimension ref="A1:I397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13453,6 +13453,72 @@
       <c r="I395" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="C396" t="n">
+        <v>355.71</v>
+      </c>
+      <c r="D396" t="n">
+        <v>355.86</v>
+      </c>
+      <c r="E396" t="n">
+        <v>365.8</v>
+      </c>
+      <c r="F396" t="n">
+        <v>365.64</v>
+      </c>
+      <c r="G396" t="n">
+        <v>349.07</v>
+      </c>
+      <c r="H396" t="n">
+        <v>354.39</v>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="C397" t="n">
+        <v>355.71</v>
+      </c>
+      <c r="D397" t="n">
+        <v>355.86</v>
+      </c>
+      <c r="E397" t="n">
+        <v>365.8</v>
+      </c>
+      <c r="F397" t="n">
+        <v>365.64</v>
+      </c>
+      <c r="G397" t="n">
+        <v>349.07</v>
+      </c>
+      <c r="H397" t="n">
+        <v>351.57</v>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13467,7 +13533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B415"/>
+  <dimension ref="A1:B417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17620,6 +17686,26 @@
       </c>
       <c r="B415" t="n">
         <v>0.78</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -17788,28 +17874,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1763181929152058</v>
+        <v>-0.1611730046754102</v>
       </c>
       <c r="J2" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K2" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01392885362314966</v>
+        <v>0.01170050758154395</v>
       </c>
       <c r="M2" t="n">
-        <v>9.546349690922151</v>
+        <v>9.576928975288542</v>
       </c>
       <c r="N2" t="n">
-        <v>120.4011570315934</v>
+        <v>120.8437611848583</v>
       </c>
       <c r="O2" t="n">
-        <v>10.97274610257585</v>
+        <v>10.99289594169154</v>
       </c>
       <c r="P2" t="n">
-        <v>315.4738405235319</v>
+        <v>315.3163750555833</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17866,28 +17952,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1008535282843455</v>
+        <v>-0.09824184590028247</v>
       </c>
       <c r="J3" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K3" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01409560892451223</v>
+        <v>0.01352585070143864</v>
       </c>
       <c r="M3" t="n">
-        <v>4.857528469195231</v>
+        <v>4.844085600398207</v>
       </c>
       <c r="N3" t="n">
-        <v>39.46917153705325</v>
+        <v>39.3028299853361</v>
       </c>
       <c r="O3" t="n">
-        <v>6.282449485435856</v>
+        <v>6.269196917096806</v>
       </c>
       <c r="P3" t="n">
-        <v>355.8091966731832</v>
+        <v>355.7821984971816</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17944,28 +18030,28 @@
         <v>0.1265</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01005077340217508</v>
+        <v>-0.01135752506845651</v>
       </c>
       <c r="J4" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K4" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003700749246580148</v>
+        <v>0.0004777066415813103</v>
       </c>
       <c r="M4" t="n">
-        <v>3.003448351621909</v>
+        <v>2.995171111046142</v>
       </c>
       <c r="N4" t="n">
-        <v>15.08568185921018</v>
+        <v>15.01752422450725</v>
       </c>
       <c r="O4" t="n">
-        <v>3.884029075484654</v>
+        <v>3.875245053478199</v>
       </c>
       <c r="P4" t="n">
-        <v>357.4131941176894</v>
+        <v>357.4267462875604</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18022,28 +18108,28 @@
         <v>0.065</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04650949959944533</v>
+        <v>0.05020854100998189</v>
       </c>
       <c r="J5" t="n">
+        <v>396</v>
+      </c>
+      <c r="K5" t="n">
         <v>394</v>
       </c>
-      <c r="K5" t="n">
-        <v>392</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.005119110985784103</v>
+        <v>0.006012457838653784</v>
       </c>
       <c r="M5" t="n">
-        <v>3.777621669515018</v>
+        <v>3.774837676751074</v>
       </c>
       <c r="N5" t="n">
-        <v>23.0499580178095</v>
+        <v>22.9980683068543</v>
       </c>
       <c r="O5" t="n">
-        <v>4.801037181465011</v>
+        <v>4.795630126151755</v>
       </c>
       <c r="P5" t="n">
-        <v>360.9534806891309</v>
+        <v>360.9148864378853</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18100,28 +18186,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03309968226138744</v>
+        <v>-0.02666767342150151</v>
       </c>
       <c r="J6" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K6" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001986938698274265</v>
+        <v>0.001297015758982667</v>
       </c>
       <c r="M6" t="n">
-        <v>4.492270038100495</v>
+        <v>4.497060735664101</v>
       </c>
       <c r="N6" t="n">
-        <v>30.42396397118129</v>
+        <v>30.46920186211474</v>
       </c>
       <c r="O6" t="n">
-        <v>5.515792234229031</v>
+        <v>5.519891471950761</v>
       </c>
       <c r="P6" t="n">
-        <v>360.1921503661264</v>
+        <v>360.1254446771393</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18178,28 +18264,28 @@
         <v>0.0658</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.05202063343164864</v>
+        <v>-0.04837961732199557</v>
       </c>
       <c r="J7" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K7" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004074125733207756</v>
+        <v>0.003560209517270096</v>
       </c>
       <c r="M7" t="n">
-        <v>4.674424623946707</v>
+        <v>4.668558234499287</v>
       </c>
       <c r="N7" t="n">
-        <v>36.40039714693152</v>
+        <v>36.2794611271432</v>
       </c>
       <c r="O7" t="n">
-        <v>6.033274164741026</v>
+        <v>6.02324340593531</v>
       </c>
       <c r="P7" t="n">
-        <v>346.8826046419777</v>
+        <v>346.8447394486078</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18256,28 +18342,28 @@
         <v>0.0572</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.03541651362550152</v>
+        <v>-0.03616287859370524</v>
       </c>
       <c r="J8" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K8" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001779957603034177</v>
+        <v>0.00187647098722743</v>
       </c>
       <c r="M8" t="n">
-        <v>4.548386960801151</v>
+        <v>4.532833744385325</v>
       </c>
       <c r="N8" t="n">
-        <v>38.70708839873358</v>
+        <v>38.52377975617397</v>
       </c>
       <c r="O8" t="n">
-        <v>6.221502101481087</v>
+        <v>6.20675275455483</v>
       </c>
       <c r="P8" t="n">
-        <v>354.644391232518</v>
+        <v>354.6521811336687</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18315,7 +18401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I395"/>
+  <dimension ref="A1:I397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36835,6 +36921,100 @@
         </is>
       </c>
     </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>-36.737589370882475,175.811190179913</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>-36.737542230733496,175.81023965697418</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>-36.73755881692691,175.80933383586384</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>-36.73769527462215,175.80845317411683</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>-36.73788102018796,175.80760179479807</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>-36.738068402127396,175.8067133771983</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>-36.73847566976138,175.80596890040889</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>-36.737589370882475,175.811190179913</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>-36.737542230733496,175.81023965697418</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>-36.73755881692691,175.80933383586384</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>-36.73769527462215,175.80845317411683</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>-36.73788102018796,175.80760179479807</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>-36.738068402127396,175.8067133771983</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>-36.73845405510071,175.80595232012976</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0162/nzd0162.xlsx
+++ b/data/nzd0162/nzd0162.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I397"/>
+  <dimension ref="A1:I398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13519,6 +13519,39 @@
       <c r="I397" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>320.8</v>
+      </c>
+      <c r="C398" t="n">
+        <v>355.75</v>
+      </c>
+      <c r="D398" t="n">
+        <v>356.81</v>
+      </c>
+      <c r="E398" t="n">
+        <v>365.14</v>
+      </c>
+      <c r="F398" t="n">
+        <v>365.38</v>
+      </c>
+      <c r="G398" t="n">
+        <v>348.06</v>
+      </c>
+      <c r="H398" t="n">
+        <v>349.69</v>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13533,7 +13566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B417"/>
+  <dimension ref="A1:B418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17706,6 +17739,16 @@
       </c>
       <c r="B417" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>-0.57</v>
       </c>
     </row>
   </sheetData>
@@ -17874,28 +17917,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1611730046754102</v>
+        <v>-0.1560371891420667</v>
       </c>
       <c r="J2" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K2" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01170050758154395</v>
+        <v>0.01101798177225011</v>
       </c>
       <c r="M2" t="n">
-        <v>9.576928975288542</v>
+        <v>9.578975615314132</v>
       </c>
       <c r="N2" t="n">
-        <v>120.8437611848583</v>
+        <v>120.7774774403735</v>
       </c>
       <c r="O2" t="n">
-        <v>10.99289594169154</v>
+        <v>10.98988068362771</v>
       </c>
       <c r="P2" t="n">
-        <v>315.3163750555833</v>
+        <v>315.2626377153941</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17952,28 +17995,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09824184590028247</v>
+        <v>-0.09692417688627659</v>
       </c>
       <c r="J3" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K3" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01352585070143864</v>
+        <v>0.01324023510783101</v>
       </c>
       <c r="M3" t="n">
-        <v>4.844085600398207</v>
+        <v>4.83738771312192</v>
       </c>
       <c r="N3" t="n">
-        <v>39.3028299853361</v>
+        <v>39.22054845682176</v>
       </c>
       <c r="O3" t="n">
-        <v>6.269196917096806</v>
+        <v>6.262631112944603</v>
       </c>
       <c r="P3" t="n">
-        <v>355.7821984971816</v>
+        <v>355.7684885177104</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18030,28 +18073,28 @@
         <v>0.1265</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01135752506845651</v>
+        <v>-0.01151934317336373</v>
       </c>
       <c r="J4" t="n">
+        <v>397</v>
+      </c>
+      <c r="K4" t="n">
         <v>396</v>
       </c>
-      <c r="K4" t="n">
-        <v>395</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0004777066415813103</v>
+        <v>0.0004942610026728023</v>
       </c>
       <c r="M4" t="n">
-        <v>2.995171111046142</v>
+        <v>2.988451925692244</v>
       </c>
       <c r="N4" t="n">
-        <v>15.01752422450725</v>
+        <v>14.97985222136503</v>
       </c>
       <c r="O4" t="n">
-        <v>3.875245053478199</v>
+        <v>3.87038140515441</v>
       </c>
       <c r="P4" t="n">
-        <v>357.4267462875604</v>
+        <v>357.4284353925499</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18108,28 +18151,28 @@
         <v>0.065</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05020854100998189</v>
+        <v>0.05169276961116108</v>
       </c>
       <c r="J5" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K5" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006012457838653784</v>
+        <v>0.006402103720663188</v>
       </c>
       <c r="M5" t="n">
-        <v>3.774837676751074</v>
+        <v>3.771849879617527</v>
       </c>
       <c r="N5" t="n">
-        <v>22.9980683068543</v>
+        <v>22.96070962679841</v>
       </c>
       <c r="O5" t="n">
-        <v>4.795630126151755</v>
+        <v>4.791733467837961</v>
       </c>
       <c r="P5" t="n">
-        <v>360.9148864378853</v>
+        <v>360.8993006919713</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18186,28 +18229,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02666767342150151</v>
+        <v>-0.02362068908779895</v>
       </c>
       <c r="J6" t="n">
+        <v>397</v>
+      </c>
+      <c r="K6" t="n">
         <v>396</v>
       </c>
-      <c r="K6" t="n">
-        <v>395</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.001297015758982667</v>
+        <v>0.001020778984161419</v>
       </c>
       <c r="M6" t="n">
-        <v>4.497060735664101</v>
+        <v>4.498751354637847</v>
       </c>
       <c r="N6" t="n">
-        <v>30.46920186211474</v>
+        <v>30.4812666848026</v>
       </c>
       <c r="O6" t="n">
-        <v>5.519891471950761</v>
+        <v>5.52098421341726</v>
       </c>
       <c r="P6" t="n">
-        <v>360.1254446771393</v>
+        <v>360.0936393581722</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18264,28 +18307,28 @@
         <v>0.0658</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04837961732199557</v>
+        <v>-0.04709615646986912</v>
       </c>
       <c r="J7" t="n">
+        <v>397</v>
+      </c>
+      <c r="K7" t="n">
         <v>396</v>
       </c>
-      <c r="K7" t="n">
-        <v>395</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.003560209517270096</v>
+        <v>0.00339262336599977</v>
       </c>
       <c r="M7" t="n">
-        <v>4.668558234499287</v>
+        <v>4.663005384814431</v>
       </c>
       <c r="N7" t="n">
-        <v>36.2794611271432</v>
+        <v>36.20351827809046</v>
       </c>
       <c r="O7" t="n">
-        <v>6.02324340593531</v>
+        <v>6.016935954295214</v>
       </c>
       <c r="P7" t="n">
-        <v>346.8447394486078</v>
+        <v>346.8313057028606</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18342,28 +18385,28 @@
         <v>0.0572</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.03616287859370524</v>
+        <v>-0.03821248455826434</v>
       </c>
       <c r="J8" t="n">
+        <v>397</v>
+      </c>
+      <c r="K8" t="n">
         <v>396</v>
       </c>
-      <c r="K8" t="n">
-        <v>395</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.00187647098722743</v>
+        <v>0.002104769920271754</v>
       </c>
       <c r="M8" t="n">
-        <v>4.532833744385325</v>
+        <v>4.532327049366532</v>
       </c>
       <c r="N8" t="n">
-        <v>38.52377975617397</v>
+        <v>38.46646421126173</v>
       </c>
       <c r="O8" t="n">
-        <v>6.20675275455483</v>
+        <v>6.202133843385012</v>
       </c>
       <c r="P8" t="n">
-        <v>354.6521811336687</v>
+        <v>354.6736339776446</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18401,7 +18444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I397"/>
+  <dimension ref="A1:I398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37015,6 +37058,53 @@
         </is>
       </c>
     </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>-36.737552190037825,175.81121024065624</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>-36.73754258512459,175.81023957613974</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>-36.737567355778054,175.80933453647836</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>-36.73768943551035,175.8084517850406</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>-36.73787885151384,175.80760069606666</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>-36.738060498032546,175.8067077794957</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>-36.7384396453254,175.80594126661563</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0162/nzd0162.xlsx
+++ b/data/nzd0162/nzd0162.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I398"/>
+  <dimension ref="A1:I400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13550,6 +13550,72 @@
         <v>349.69</v>
       </c>
       <c r="I398" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>317.5</v>
+      </c>
+      <c r="C399" t="n">
+        <v>356.42</v>
+      </c>
+      <c r="D399" t="n">
+        <v>357.28</v>
+      </c>
+      <c r="E399" t="n">
+        <v>365.18</v>
+      </c>
+      <c r="F399" t="n">
+        <v>365.52</v>
+      </c>
+      <c r="G399" t="n">
+        <v>347.52</v>
+      </c>
+      <c r="H399" t="n">
+        <v>348.95</v>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>315.21</v>
+      </c>
+      <c r="C400" t="n">
+        <v>356.38</v>
+      </c>
+      <c r="D400" t="n">
+        <v>356.68</v>
+      </c>
+      <c r="E400" t="n">
+        <v>364.3</v>
+      </c>
+      <c r="F400" t="n">
+        <v>364.78</v>
+      </c>
+      <c r="G400" t="n">
+        <v>346.16</v>
+      </c>
+      <c r="H400" t="n">
+        <v>347.81</v>
+      </c>
+      <c r="I400" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13566,7 +13632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B418"/>
+  <dimension ref="A1:B420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17749,6 +17815,26 @@
       </c>
       <c r="B418" t="n">
         <v>-0.57</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>-0.67</v>
       </c>
     </row>
   </sheetData>
@@ -17917,28 +18003,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1560371891420667</v>
+        <v>-0.150574652136349</v>
       </c>
       <c r="J2" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K2" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01101798177225011</v>
+        <v>0.01037718068487137</v>
       </c>
       <c r="M2" t="n">
-        <v>9.578975615314132</v>
+        <v>9.558161996340155</v>
       </c>
       <c r="N2" t="n">
-        <v>120.7774774403735</v>
+        <v>120.3081163750319</v>
       </c>
       <c r="O2" t="n">
-        <v>10.98988068362771</v>
+        <v>10.96850565824862</v>
       </c>
       <c r="P2" t="n">
-        <v>315.2626377153941</v>
+        <v>315.2053396832706</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17995,28 +18081,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09692417688627659</v>
+        <v>-0.09367507985665981</v>
       </c>
       <c r="J3" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K3" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01324023510783101</v>
+        <v>0.01250399504000166</v>
       </c>
       <c r="M3" t="n">
-        <v>4.83738771312192</v>
+        <v>4.826651766939526</v>
       </c>
       <c r="N3" t="n">
-        <v>39.22054845682176</v>
+        <v>39.07520415953939</v>
       </c>
       <c r="O3" t="n">
-        <v>6.262631112944603</v>
+        <v>6.251016250142003</v>
       </c>
       <c r="P3" t="n">
-        <v>355.7684885177104</v>
+        <v>355.7345900528207</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18073,28 +18159,28 @@
         <v>0.1265</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01151934317336373</v>
+        <v>-0.01166025289487702</v>
       </c>
       <c r="J4" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K4" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004942610026728023</v>
+        <v>0.0005122865626906448</v>
       </c>
       <c r="M4" t="n">
-        <v>2.988451925692244</v>
+        <v>2.974964935985688</v>
       </c>
       <c r="N4" t="n">
-        <v>14.97985222136503</v>
+        <v>14.90511471742299</v>
       </c>
       <c r="O4" t="n">
-        <v>3.87038140515441</v>
+        <v>3.860714275548371</v>
       </c>
       <c r="P4" t="n">
-        <v>357.4284353925499</v>
+        <v>357.4299131653156</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18151,28 +18237,28 @@
         <v>0.065</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05169276961116108</v>
+        <v>0.05419781931216133</v>
       </c>
       <c r="J5" t="n">
+        <v>399</v>
+      </c>
+      <c r="K5" t="n">
         <v>397</v>
       </c>
-      <c r="K5" t="n">
-        <v>395</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.006402103720663188</v>
+        <v>0.007105097653588466</v>
       </c>
       <c r="M5" t="n">
-        <v>3.771849879617527</v>
+        <v>3.763848167773556</v>
       </c>
       <c r="N5" t="n">
-        <v>22.96070962679841</v>
+        <v>22.8760139816488</v>
       </c>
       <c r="O5" t="n">
-        <v>4.791733467837961</v>
+        <v>4.782887619592248</v>
       </c>
       <c r="P5" t="n">
-        <v>360.8993006919713</v>
+        <v>360.8729282700084</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18229,28 +18315,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02362068908779895</v>
+        <v>-0.0178706554277571</v>
       </c>
       <c r="J6" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K6" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001020778984161419</v>
+        <v>0.000588223391793985</v>
       </c>
       <c r="M6" t="n">
-        <v>4.498751354637847</v>
+        <v>4.500789571253899</v>
       </c>
       <c r="N6" t="n">
-        <v>30.4812666848026</v>
+        <v>30.48863785972672</v>
       </c>
       <c r="O6" t="n">
-        <v>5.52098421341726</v>
+        <v>5.521651732926183</v>
       </c>
       <c r="P6" t="n">
-        <v>360.0936393581722</v>
+        <v>360.0334581648092</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18307,28 +18393,28 @@
         <v>0.0658</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04709615646986912</v>
+        <v>-0.04580936431610268</v>
       </c>
       <c r="J7" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K7" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00339262336599977</v>
+        <v>0.003246736871922007</v>
       </c>
       <c r="M7" t="n">
-        <v>4.663005384814431</v>
+        <v>4.645763199521156</v>
       </c>
       <c r="N7" t="n">
-        <v>36.20351827809046</v>
+        <v>36.03189558711608</v>
       </c>
       <c r="O7" t="n">
-        <v>6.016935954295214</v>
+        <v>6.00265737712191</v>
       </c>
       <c r="P7" t="n">
-        <v>346.8313057028606</v>
+        <v>346.817807091868</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18385,28 +18471,28 @@
         <v>0.0572</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.03821248455826434</v>
+        <v>-0.04356476579124489</v>
       </c>
       <c r="J8" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K8" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002104769920271754</v>
+        <v>0.002755762934216532</v>
       </c>
       <c r="M8" t="n">
-        <v>4.532327049366532</v>
+        <v>4.537818813424913</v>
       </c>
       <c r="N8" t="n">
-        <v>38.46646421126173</v>
+        <v>38.4121357358499</v>
       </c>
       <c r="O8" t="n">
-        <v>6.202133843385012</v>
+        <v>6.19775247455478</v>
       </c>
       <c r="P8" t="n">
-        <v>354.6736339776446</v>
+        <v>354.7298132856109</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18444,7 +18530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I398"/>
+  <dimension ref="A1:I400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37105,6 +37191,100 @@
         </is>
       </c>
     </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>-36.73752492408332,175.81122495185622</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>-36.73754852117545,175.81023822216304</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>-36.737571580262276,175.80933488309822</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>-36.73768978939591,175.80845186922704</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>-36.73788001926144,175.80760128769128</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>-36.7380562720807,175.80670478666508</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>-36.73843397339222,175.8059369157655</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>-36.737506003162494,175.8112351605316</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>-36.73754816678436,175.81023830299748</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>-36.73756618730368,175.80933444060474</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>-36.737682003913456,175.80845001712575</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>-36.73787384688118,175.8075981605329</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>-36.73804562894236,175.80669724916729</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>-36.73842523554885,175.80593021310577</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
